--- a/results/Int Task Remove ACC -0.4/Rando_3_permute.xlsx
+++ b/results/Int Task Remove ACC -0.4/Rando_3_permute.xlsx
@@ -440,27 +440,27 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7708406779539692</v>
+        <v>0.8120155905790811</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7710913942222517</v>
+        <v>0.7975218280634002</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7770502452581339</v>
+        <v>0.7858904543494172</v>
       </c>
     </row>
     <row r="5">
@@ -470,857 +470,857 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7936603322482683</v>
+        <v>0.7945261176201103</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7966136303035618</v>
+        <v>0.7907684158346739</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7851420636042656</v>
+        <v>0.7928915406076246</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7851420636042656</v>
+        <v>0.7945033903067114</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.769203058702682</v>
+        <v>0.7887301158377162</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7798936648061288</v>
+        <v>0.7383581574054356</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7794149595829627</v>
+        <v>0.7656747775139182</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7767676749600483</v>
+        <v>0.7706209209393717</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7716132276543086</v>
+        <v>0.770806497506259</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7713299415353285</v>
+        <v>0.7714935066097112</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.779311165553267</v>
+        <v>0.7678236718390692</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7792748376428733</v>
+        <v>0.7649582407985698</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7757451248123207</v>
+        <v>0.7494358436575584</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7738303039196563</v>
+        <v>0.719810522209238</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7753444440666502</v>
+        <v>0.7382180354653463</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7841300718147313</v>
+        <v>0.7382180354653463</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7859827952448017</v>
+        <v>0.7142879640085253</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7844360852471103</v>
+        <v>0.7157793768421203</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7649181548284805</v>
+        <v>0.7131419347565046</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7584056163307379</v>
+        <v>0.712988928040315</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7160612313193115</v>
+        <v>0.6933111906069982</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7433785672486887</v>
+        <v>0.6679260342269762</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7299830529403237</v>
+        <v>0.6597402643884474</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7181396172863588</v>
+        <v>0.6607204021481785</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7233788893680912</v>
+        <v>0.6628662542345281</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7309336630881587</v>
+        <v>0.5992374717921829</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7246491135452998</v>
+        <v>0.5998040440301432</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7255186569768378</v>
+        <v>0.6041510453669388</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7319009160717898</v>
+        <v>0.5915334494156217</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7287749262257091</v>
+        <v>0.5941155943371409</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7298853433882309</v>
+        <v>0.6231288889207032</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7325947254737392</v>
+        <v>0.6231288889207032</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7386906562109095</v>
+        <v>0.6232788533980913</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.731888747116584</v>
+        <v>0.6254572753351384</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7395056182992454</v>
+        <v>0.6373681771084057</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.733471785024669</v>
+        <v>0.6713601849681191</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.733471785024669</v>
+        <v>0.6732061080996923</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7380172477044519</v>
+        <v>0.6738310197405507</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7244839378739045</v>
+        <v>0.6689204884045963</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7228524031002204</v>
+        <v>0.6556318103647286</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7174502817649996</v>
+        <v>0.6535525296215634</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7126405022199396</v>
+        <v>0.6409084482971515</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6716525978035035</v>
+        <v>0.6425104554589396</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6801875092833023</v>
+        <v>0.6123624058024442</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6903797250889855</v>
+        <v>0.6110989819237329</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6908258604614539</v>
+        <v>0.6222092380265534</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6840368361432286</v>
+        <v>0.614918781171763</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6840368361432286</v>
+        <v>0.614918781171763</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6562194993190754</v>
+        <v>0.5510165551477365</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6562422266324743</v>
+        <v>0.5465748864976494</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.6562520691697731</v>
+        <v>0.5107285446108529</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.6589766624492885</v>
+        <v>0.5247428860824733</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.6596280594632418</v>
+        <v>0.5163087263935691</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.6611194722968365</v>
+        <v>0.5277840511525611</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.6877809373316702</v>
+        <v>0.5246550190676791</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.6680842306446504</v>
+        <v>0.5186931257929953</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.6014119567143106</v>
+        <v>0.5073094261084934</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.6001159629849016</v>
+        <v>0.5064042705874563</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5854274971859291</v>
+        <v>0.5029593825328964</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5721456194445588</v>
+        <v>0.5046818265601763</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5317727841316824</v>
+        <v>0.5046818265601763</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.6226160032498268</v>
+        <v>0.512330551772641</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5222849360861419</v>
+        <v>0.5241407017550138</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5222849360861419</v>
+        <v>0.5234536926515616</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5177326731078616</v>
+        <v>0.5218092731017772</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5184620945993103</v>
+        <v>0.5335800529349551</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5050597799924481</v>
+        <v>0.5224864396679307</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5048219485002657</v>
+        <v>0.5224864396679307</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4977557225406631</v>
+        <v>0.5210601665357312</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5005431291036669</v>
+        <v>0.5042553762623054</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4972278046310032</v>
+        <v>0.5060300752148804</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4972800595562984</v>
+        <v>0.5060300752148804</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4953825973203245</v>
+        <v>0.5076517674512661</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.499303148359249</v>
+        <v>0.5057990440211955</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.499303148359249</v>
+        <v>0.5029987526820914</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4979420149284448</v>
+        <v>0.502823018652503</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4938813419494308</v>
+        <v>0.5019178631314659</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4938813419494308</v>
+        <v>0.5008498583569405</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4946107634408795</v>
+        <v>0.5014164305949008</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4945781935901818</v>
+        <v>0.5019178631314659</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4975739040334718</v>
+        <v>0.5022011492504461</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4970073317955114</v>
+        <v>0.5024844353694262</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4970073317955114</v>
+        <v>0.5015368674603927</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5026374420856158</v>
+        <v>0.5002181464175849</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5013088785055091</v>
+        <v>0.5001530067161896</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5004166077605723</v>
+        <v>0.4999348602986047</v>
       </c>
     </row>
   </sheetData>
